--- a/backend/data/financials_by_company/002354.SZ.xlsx
+++ b/backend/data/financials_by_company/002354.SZ.xlsx
@@ -697,670 +697,670 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-23949617.9975</v>
+        <v>-7931034.815</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>27771542.38</v>
+        <v>119400554.6</v>
       </c>
       <c r="E2" t="n">
-        <v>-95798471.98999999</v>
+        <v>-31724139.26</v>
       </c>
       <c r="F2" t="n">
-        <v>-95798471.98999999</v>
+        <v>-31724139.26</v>
       </c>
       <c r="G2" t="n">
-        <v>-117947982.33</v>
+        <v>42720721.51</v>
       </c>
       <c r="H2" t="n">
-        <v>23414747.1</v>
+        <v>32447691.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1216978266.5</v>
+        <v>1424963824.82</v>
       </c>
       <c r="J2" t="n">
-        <v>-68026929.61</v>
+        <v>87676415.34</v>
       </c>
       <c r="K2" t="n">
-        <v>-91441676.70999999</v>
+        <v>55228723.91</v>
       </c>
       <c r="L2" t="n">
-        <v>1823481.92</v>
+        <v>-195066.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1218204.45</v>
+        <v>1066878.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4094243.14</v>
+        <v>2383687.74</v>
       </c>
       <c r="O2" t="n">
-        <v>-46099128.3375</v>
+        <v>66513825.955</v>
       </c>
       <c r="P2" t="n">
-        <v>-117947982.33</v>
+        <v>42720721.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>1560919030.49</v>
+        <v>1809247581.86</v>
       </c>
       <c r="R2" t="n">
-        <v>23458385.52</v>
+        <v>33635184.65</v>
       </c>
       <c r="S2" t="n">
-        <v>-253407588.84</v>
+        <v>20133145.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1654249402</v>
+        <v>1662284884</v>
       </c>
       <c r="U2" t="n">
-        <v>1654249402</v>
+        <v>1662284884</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0713</v>
+        <v>0.0257</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0713</v>
+        <v>0.0257</v>
       </c>
       <c r="X2" t="n">
-        <v>-117947982.33</v>
+        <v>42720721.51</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-117947982.33</v>
+        <v>42720721.51</v>
       </c>
       <c r="AA2" t="n">
-        <v>-8107109.79</v>
+        <v>-14518474.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>-109840872.54</v>
+        <v>57239196.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>-109840872.54</v>
+        <v>57239196.37</v>
       </c>
       <c r="AD2" t="n">
-        <v>17180991.38</v>
+        <v>-3077350.56</v>
       </c>
       <c r="AE2" t="n">
-        <v>-92659881.16</v>
+        <v>54161845.81</v>
       </c>
       <c r="AF2" t="n">
-        <v>160747707.68</v>
+        <v>34028700.51</v>
       </c>
       <c r="AG2" t="n">
-        <v>-112835946.53</v>
+        <v>-90755789.29000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2054851.98</v>
+        <v>-141619.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>36548568.08</v>
+        <v>-473389.63</v>
       </c>
       <c r="AJ2" t="n">
-        <v>78342230.43000001</v>
+        <v>91370797.97</v>
       </c>
       <c r="AK2" t="n">
-        <v>1823481.92</v>
+        <v>-195066.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>1052556.77</v>
+        <v>1511875.86</v>
       </c>
       <c r="AM2" t="n">
-        <v>1218204.45</v>
+        <v>1066878.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>4094243.14</v>
+        <v>2383687.74</v>
       </c>
       <c r="AO2" t="n">
-        <v>17656245.93</v>
+        <v>-45170150.06</v>
       </c>
       <c r="AP2" t="n">
-        <v>343940763.99</v>
+        <v>384283757.04</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3668984.3</v>
+        <v>1240395.46</v>
       </c>
       <c r="AR2" t="n">
-        <v>7071679.34</v>
+        <v>13869722.77</v>
       </c>
       <c r="AS2" t="n">
-        <v>511376.04</v>
+        <v>7454755.58</v>
       </c>
       <c r="AT2" t="n">
-        <v>6560303.3</v>
+        <v>6414967.19</v>
       </c>
       <c r="AU2" t="n">
-        <v>51998959.59</v>
+        <v>88121712.43000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>86412761.09</v>
+        <v>129300211.44</v>
       </c>
       <c r="AW2" t="n">
-        <v>48995524.13</v>
+        <v>83870521.81</v>
       </c>
       <c r="AX2" t="n">
-        <v>37417236.96</v>
+        <v>45429689.63</v>
       </c>
       <c r="AY2" t="n">
-        <v>23458385.52</v>
+        <v>33635184.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>361597009.92</v>
+        <v>339113606.98</v>
       </c>
       <c r="BA2" t="n">
-        <v>1216978266.5</v>
+        <v>1424963824.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>1578575276.42</v>
+        <v>1764077431.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1578575276.42</v>
+        <v>1764077431.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-78189242.3175</v>
+        <v>-38268026.625</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-664630020.25</v>
+        <v>-64693587.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-312756969.27</v>
+        <v>-153072106.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-312756969.27</v>
+        <v>-153072106.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-1087055509.33</v>
+        <v>-282387596.22</v>
       </c>
       <c r="H3" t="n">
-        <v>28354494.88</v>
+        <v>24897652.88</v>
       </c>
       <c r="I3" t="n">
-        <v>1373221845.17</v>
+        <v>1450803527.23</v>
       </c>
       <c r="J3" t="n">
-        <v>-977386989.52</v>
+        <v>-217765693.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-1005741484.4</v>
+        <v>-242663346.68</v>
       </c>
       <c r="L3" t="n">
-        <v>4463363.63</v>
+        <v>2245587.74</v>
       </c>
       <c r="M3" t="n">
-        <v>1146488.58</v>
+        <v>1247377.58</v>
       </c>
       <c r="N3" t="n">
-        <v>6282110.01</v>
+        <v>3704147.9</v>
       </c>
       <c r="O3" t="n">
-        <v>-852487782.3775001</v>
+        <v>-167583516.345</v>
       </c>
       <c r="P3" t="n">
-        <v>-1087055509.33</v>
+        <v>-282387596.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1739685289.53</v>
+        <v>1770030800.05</v>
       </c>
       <c r="R3" t="n">
-        <v>23653995.22</v>
+        <v>21063870.7</v>
       </c>
       <c r="S3" t="n">
-        <v>-781294891.84</v>
+        <v>-204002850.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1654574596</v>
+        <v>1658177312</v>
       </c>
       <c r="U3" t="n">
-        <v>1654574596</v>
+        <v>1658177312</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.657</v>
+        <v>-0.1703</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.657</v>
+        <v>-0.1703</v>
       </c>
       <c r="X3" t="n">
-        <v>-1087055509.33</v>
+        <v>-282387596.22</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1087055509.33</v>
+        <v>-282387596.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>-17481879.49</v>
+        <v>-20832175.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1069573629.84</v>
+        <v>-261555420.97</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1069573629.84</v>
+        <v>-261555420.97</v>
       </c>
       <c r="AD3" t="n">
-        <v>62685656.86</v>
+        <v>17644696.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1006887972.98</v>
+        <v>-243910724.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>-225593081.14</v>
+        <v>-39907873.28</v>
       </c>
       <c r="AG3" t="n">
-        <v>-308869649.38</v>
+        <v>-156515619.95</v>
       </c>
       <c r="AH3" t="n">
-        <v>-11713795.9</v>
+        <v>31059.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>5586118.39</v>
+        <v>1751133.08</v>
       </c>
       <c r="AJ3" t="n">
-        <v>314997326.89</v>
+        <v>154733427.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>4463363.63</v>
+        <v>2245587.74</v>
       </c>
       <c r="AL3" t="n">
-        <v>672257.8</v>
+        <v>211182.58</v>
       </c>
       <c r="AM3" t="n">
-        <v>1146488.58</v>
+        <v>1247377.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>6282110.01</v>
+        <v>3704147.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>21689172.18</v>
+        <v>-27371480.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>366463444.36</v>
+        <v>319227272.82</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1885138.03</v>
+        <v>3054544.94</v>
       </c>
       <c r="AR3" t="n">
-        <v>7788686.68</v>
+        <v>7235844.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>365776.74</v>
+        <v>529212.85</v>
       </c>
       <c r="AT3" t="n">
-        <v>7422909.94</v>
+        <v>6706631.44</v>
       </c>
       <c r="AU3" t="n">
-        <v>61198205.27</v>
+        <v>62740080.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>105122667.27</v>
+        <v>92717429.95</v>
       </c>
       <c r="AW3" t="n">
-        <v>56694384.94</v>
+        <v>63336502.12</v>
       </c>
       <c r="AX3" t="n">
-        <v>48428282.33</v>
+        <v>29380927.83</v>
       </c>
       <c r="AY3" t="n">
-        <v>23653995.22</v>
+        <v>21063870.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>388152616.54</v>
+        <v>291855792.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>1373221845.17</v>
+        <v>1450803527.23</v>
       </c>
       <c r="BB3" t="n">
-        <v>1761374461.71</v>
+        <v>1742659319.93</v>
       </c>
       <c r="BC3" t="n">
-        <v>1761374461.71</v>
+        <v>1742659319.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-38268026.625</v>
+        <v>-78189242.3175</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-64693587.3</v>
+        <v>-664630020.25</v>
       </c>
       <c r="E4" t="n">
-        <v>-153072106.5</v>
+        <v>-312756969.27</v>
       </c>
       <c r="F4" t="n">
-        <v>-153072106.5</v>
+        <v>-312756969.27</v>
       </c>
       <c r="G4" t="n">
-        <v>-282387596.22</v>
+        <v>-1087055509.33</v>
       </c>
       <c r="H4" t="n">
-        <v>24897652.88</v>
+        <v>28354494.88</v>
       </c>
       <c r="I4" t="n">
-        <v>1450803527.23</v>
+        <v>1373221845.17</v>
       </c>
       <c r="J4" t="n">
-        <v>-217765693.8</v>
+        <v>-977386989.52</v>
       </c>
       <c r="K4" t="n">
-        <v>-242663346.68</v>
+        <v>-1005741484.4</v>
       </c>
       <c r="L4" t="n">
-        <v>2245587.74</v>
+        <v>4463363.63</v>
       </c>
       <c r="M4" t="n">
-        <v>1247377.58</v>
+        <v>1146488.58</v>
       </c>
       <c r="N4" t="n">
-        <v>3704147.9</v>
+        <v>6282110.01</v>
       </c>
       <c r="O4" t="n">
-        <v>-167583516.345</v>
+        <v>-852487782.3775001</v>
       </c>
       <c r="P4" t="n">
-        <v>-282387596.22</v>
+        <v>-1087055509.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>1770030800.05</v>
+        <v>1739685289.53</v>
       </c>
       <c r="R4" t="n">
-        <v>21063870.7</v>
+        <v>23653995.22</v>
       </c>
       <c r="S4" t="n">
-        <v>-204002850.98</v>
+        <v>-781294891.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1658177312</v>
+        <v>1654574596</v>
       </c>
       <c r="U4" t="n">
-        <v>1658177312</v>
+        <v>1654574596</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1703</v>
+        <v>-0.657</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1703</v>
+        <v>-0.657</v>
       </c>
       <c r="X4" t="n">
-        <v>-282387596.22</v>
+        <v>-1087055509.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-282387596.22</v>
+        <v>-1087055509.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>-20832175.25</v>
+        <v>-17481879.49</v>
       </c>
       <c r="AB4" t="n">
-        <v>-261555420.97</v>
+        <v>-1069573629.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>-261555420.97</v>
+        <v>-1069573629.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>17644696.71</v>
+        <v>62685656.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>-243910724.26</v>
+        <v>-1006887972.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>-39907873.28</v>
+        <v>-225593081.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>-156515619.95</v>
+        <v>-308869649.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>31059.56</v>
+        <v>-11713795.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1751133.08</v>
+        <v>5586118.39</v>
       </c>
       <c r="AJ4" t="n">
-        <v>154733427.31</v>
+        <v>314997326.89</v>
       </c>
       <c r="AK4" t="n">
-        <v>2245587.74</v>
+        <v>4463363.63</v>
       </c>
       <c r="AL4" t="n">
-        <v>211182.58</v>
+        <v>672257.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>1247377.58</v>
+        <v>1146488.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>3704147.9</v>
+        <v>6282110.01</v>
       </c>
       <c r="AO4" t="n">
-        <v>-27371480.12</v>
+        <v>21689172.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>319227272.82</v>
+        <v>366463444.36</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3054544.94</v>
+        <v>1885138.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>7235844.29</v>
+        <v>7788686.68</v>
       </c>
       <c r="AS4" t="n">
-        <v>529212.85</v>
+        <v>365776.74</v>
       </c>
       <c r="AT4" t="n">
-        <v>6706631.44</v>
+        <v>7422909.94</v>
       </c>
       <c r="AU4" t="n">
-        <v>62740080.64</v>
+        <v>61198205.27</v>
       </c>
       <c r="AV4" t="n">
-        <v>92717429.95</v>
+        <v>105122667.27</v>
       </c>
       <c r="AW4" t="n">
-        <v>63336502.12</v>
+        <v>56694384.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>29380927.83</v>
+        <v>48428282.33</v>
       </c>
       <c r="AY4" t="n">
-        <v>21063870.7</v>
+        <v>23653995.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>291855792.7</v>
+        <v>388152616.54</v>
       </c>
       <c r="BA4" t="n">
-        <v>1450803527.23</v>
+        <v>1373221845.17</v>
       </c>
       <c r="BB4" t="n">
-        <v>1742659319.93</v>
+        <v>1761374461.71</v>
       </c>
       <c r="BC4" t="n">
-        <v>1742659319.93</v>
+        <v>1761374461.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-7931034.815</v>
+        <v>-23949617.9975</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>119400554.6</v>
+        <v>27771542.38</v>
       </c>
       <c r="E5" t="n">
-        <v>-31724139.26</v>
+        <v>-95798471.98999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-31724139.26</v>
+        <v>-95798471.98999999</v>
       </c>
       <c r="G5" t="n">
-        <v>42720721.51</v>
+        <v>-117947982.33</v>
       </c>
       <c r="H5" t="n">
-        <v>32447691.43</v>
+        <v>23414747.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1424963824.82</v>
+        <v>1216978266.5</v>
       </c>
       <c r="J5" t="n">
-        <v>87676415.34</v>
+        <v>-68026929.61</v>
       </c>
       <c r="K5" t="n">
-        <v>55228723.91</v>
+        <v>-91441676.70999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-195066.22</v>
+        <v>1823481.92</v>
       </c>
       <c r="M5" t="n">
-        <v>1066878.1</v>
+        <v>1218204.45</v>
       </c>
       <c r="N5" t="n">
-        <v>2383687.74</v>
+        <v>4094243.14</v>
       </c>
       <c r="O5" t="n">
-        <v>66513825.955</v>
+        <v>-46099128.3375</v>
       </c>
       <c r="P5" t="n">
-        <v>42720721.51</v>
+        <v>-117947982.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>1809247581.86</v>
+        <v>1560919030.49</v>
       </c>
       <c r="R5" t="n">
-        <v>33635184.65</v>
+        <v>23458385.52</v>
       </c>
       <c r="S5" t="n">
-        <v>20133145.3</v>
+        <v>-253407588.84</v>
       </c>
       <c r="T5" t="n">
-        <v>1662284884</v>
+        <v>1654249402</v>
       </c>
       <c r="U5" t="n">
-        <v>1662284884</v>
+        <v>1654249402</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0257</v>
+        <v>-0.0713</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0257</v>
+        <v>-0.0713</v>
       </c>
       <c r="X5" t="n">
-        <v>42720721.51</v>
+        <v>-117947982.33</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>42720721.51</v>
+        <v>-117947982.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>-14518474.86</v>
+        <v>-8107109.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>57239196.37</v>
+        <v>-109840872.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>57239196.37</v>
+        <v>-109840872.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3077350.56</v>
+        <v>17180991.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>54161845.81</v>
+        <v>-92659881.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>34028700.51</v>
+        <v>160747707.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>-90755789.29000001</v>
+        <v>-112835946.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>-141619.05</v>
+        <v>-2054851.98</v>
       </c>
       <c r="AI5" t="n">
-        <v>-473389.63</v>
+        <v>36548568.08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>91370797.97</v>
+        <v>78342230.43000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>-195066.22</v>
+        <v>1823481.92</v>
       </c>
       <c r="AL5" t="n">
-        <v>1511875.86</v>
+        <v>1052556.77</v>
       </c>
       <c r="AM5" t="n">
-        <v>1066878.1</v>
+        <v>1218204.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>2383687.74</v>
+        <v>4094243.14</v>
       </c>
       <c r="AO5" t="n">
-        <v>-45170150.06</v>
+        <v>17656245.93</v>
       </c>
       <c r="AP5" t="n">
-        <v>384283757.04</v>
+        <v>343940763.99</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1240395.46</v>
+        <v>3668984.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>13869722.77</v>
+        <v>7071679.34</v>
       </c>
       <c r="AS5" t="n">
-        <v>7454755.58</v>
+        <v>511376.04</v>
       </c>
       <c r="AT5" t="n">
-        <v>6414967.19</v>
+        <v>6560303.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>88121712.43000001</v>
+        <v>51998959.59</v>
       </c>
       <c r="AV5" t="n">
-        <v>129300211.44</v>
+        <v>86412761.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>83870521.81</v>
+        <v>48995524.13</v>
       </c>
       <c r="AX5" t="n">
-        <v>45429689.63</v>
+        <v>37417236.96</v>
       </c>
       <c r="AY5" t="n">
-        <v>33635184.65</v>
+        <v>23458385.52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>339113606.98</v>
+        <v>361597009.92</v>
       </c>
       <c r="BA5" t="n">
-        <v>1424963824.82</v>
+        <v>1216978266.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1764077431.8</v>
+        <v>1578575276.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>1764077431.8</v>
+        <v>1578575276.42</v>
       </c>
     </row>
   </sheetData>
@@ -1721,84 +1721,210 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1662283291</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1662283291</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16144050.86</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2065256003.59</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2687208070.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>974739557.42</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2065256003.59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1853092.27</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2686465217.95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2686465217.95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2761320716.19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>74855498.23999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2686465217.95</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-5911320653.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7024377847.29</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1662283291</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1662283291</v>
+      </c>
+      <c r="S2" t="n">
+        <v>824910761.0599999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>458244305.55</v>
+      </c>
+      <c r="U2" t="n">
+        <v>453909241</v>
+      </c>
+      <c r="V2" t="n">
+        <v>265933.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2216038.58</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1853092.27</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1853092.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>366666455.51</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6323166.49</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14290958.59</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>742852.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>267306786.35</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>60149180.48</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9091214.48</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>19631124.13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>178435267.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3586231477.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2244825464.32</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3176001.9</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>8349035.18</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>794630.9399999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>177153288.35</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>177153288.35</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1349193737.49</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>-186840521.09</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>729941163.87</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>621209214.36</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2187926.81</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>619021287.55</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>84949556.09999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-51995866.19</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>136945422.29</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>28977791.49</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>31126135.05</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>76841495.75</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1341406012.93</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16099684.28</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>28059844.9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>24134107.28</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>12068939.6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>11292780.96</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>772386.72</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>67975085.45999999</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>220220873.8</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>984916417.21</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>582068791.23</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>402847625.98</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>8968598.07</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>393879027.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1654585820</v>
@@ -1807,43 +1933,43 @@
         <v>1654585820</v>
       </c>
       <c r="D3" t="n">
-        <v>23047428.34</v>
+        <v>24203977.7</v>
       </c>
       <c r="E3" t="n">
-        <v>672921877.8</v>
+        <v>1733025673.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1229915698.63</v>
+        <v>2354020980.31</v>
       </c>
       <c r="G3" t="n">
-        <v>478888491.95</v>
+        <v>419011356.49</v>
       </c>
       <c r="H3" t="n">
-        <v>672921877.8</v>
+        <v>1733025673.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6983961.98</v>
+        <v>14305957.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1220694471.03</v>
+        <v>2353595485.51</v>
       </c>
       <c r="K3" t="n">
-        <v>1220694471.03</v>
+        <v>2353595485.51</v>
       </c>
       <c r="L3" t="n">
-        <v>1262267620.91</v>
+        <v>2401250237.68</v>
       </c>
       <c r="M3" t="n">
-        <v>41573149.88</v>
+        <v>47654752.17</v>
       </c>
       <c r="N3" t="n">
-        <v>1220694471.03</v>
+        <v>2353595485.51</v>
       </c>
       <c r="O3" t="n">
-        <v>-7443173065.25</v>
+        <v>-6192552601.83</v>
       </c>
       <c r="P3" t="n">
-        <v>7164346760.66</v>
+        <v>6991285559.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1654585820</v>
@@ -1852,157 +1978,157 @@
         <v>1654585820</v>
       </c>
       <c r="S3" t="n">
-        <v>503574361.78</v>
+        <v>366724092.11</v>
       </c>
       <c r="T3" t="n">
-        <v>15900594.64</v>
+        <v>24616759.61</v>
       </c>
       <c r="U3" t="n">
         <v>4618000</v>
       </c>
       <c r="V3" t="n">
-        <v>1157296.67</v>
+        <v>243886.61</v>
       </c>
       <c r="W3" t="n">
-        <v>3141335.99</v>
+        <v>5448915.72</v>
       </c>
       <c r="X3" t="n">
-        <v>6983961.98</v>
+        <v>14305957.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>6983961.98</v>
+        <v>14305957.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>487673767.14</v>
+        <v>342107332.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2226267.43</v>
+        <v>2334899.59</v>
       </c>
       <c r="AB3" t="n">
-        <v>16063466.36</v>
+        <v>9898020.42</v>
       </c>
       <c r="AC3" t="n">
-        <v>9221227.6</v>
+        <v>425494.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>428989894.82</v>
+        <v>279530165.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>76905198.63</v>
+        <v>69431911.39</v>
       </c>
       <c r="AF3" t="n">
         <v>7768642.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>29291739.25</v>
+        <v>22890769.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>315024314.46</v>
+        <v>179438842.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>1765841982.69</v>
+        <v>2767974329.79</v>
       </c>
       <c r="AJ3" t="n">
-        <v>799279723.6</v>
+        <v>2006855640.8</v>
       </c>
       <c r="AK3" t="n">
         <v>3176001.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>5661921.96</v>
+        <v>7157289.37</v>
       </c>
       <c r="AM3" t="n">
-        <v>6643058.17</v>
+        <v>4747432.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>67892772.90000001</v>
+        <v>181566299.24</v>
       </c>
       <c r="AO3" t="n">
-        <v>67892772.90000001</v>
+        <v>181566299.24</v>
       </c>
       <c r="AP3" t="n">
-        <v>83243428.48</v>
+        <v>1096478240.11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25740729.23</v>
+        <v>9067043.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>547772593.23</v>
+        <v>620569812.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>3749785.03</v>
+        <v>4985443.94</v>
       </c>
       <c r="AT3" t="n">
-        <v>544022808.2</v>
+        <v>615584368.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>59149217.73</v>
+        <v>84093522.19</v>
       </c>
       <c r="AV3" t="n">
-        <v>-55697255.63</v>
+        <v>-53611893.76</v>
       </c>
       <c r="AW3" t="n">
-        <v>114846473.36</v>
+        <v>137705415.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>38967876.9</v>
+        <v>41831776.53</v>
       </c>
       <c r="AY3" t="n">
-        <v>29253378.67</v>
+        <v>29727912.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>46625217.79</v>
+        <v>66145726.72</v>
       </c>
       <c r="BA3" t="n">
-        <v>966562259.09</v>
+        <v>761118688.99</v>
       </c>
       <c r="BB3" t="n">
-        <v>88252633.48999999</v>
+        <v>23453515.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>47633178.43</v>
+        <v>21491605.97</v>
       </c>
       <c r="BD3" t="n">
-        <v>16649936.92</v>
+        <v>24827793.76</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>3861586.25</v>
+        <v>6598713.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>12748195.26</v>
+        <v>16813684.97</v>
       </c>
       <c r="BH3" t="n">
-        <v>40155.41</v>
+        <v>1415395.23</v>
       </c>
       <c r="BI3" t="n">
-        <v>18474075.46</v>
+        <v>50308437.57</v>
       </c>
       <c r="BJ3" t="n">
-        <v>455083441.58</v>
+        <v>307815661.06</v>
       </c>
       <c r="BK3" t="n">
-        <v>-121849136.28</v>
+        <v>-147978214.55</v>
       </c>
       <c r="BL3" t="n">
-        <v>576932577.86</v>
+        <v>455793875.61</v>
       </c>
       <c r="BM3" t="n">
-        <v>340468993.21</v>
+        <v>333221675.39</v>
       </c>
       <c r="BN3" t="n">
-        <v>29725574.54</v>
+        <v>12000000</v>
       </c>
       <c r="BO3" t="n">
-        <v>310743418.67</v>
+        <v>321221675.39</v>
       </c>
       <c r="BP3" t="n">
-        <v>4370764.69</v>
+        <v>11780104.54</v>
       </c>
       <c r="BQ3" t="n">
-        <v>306372653.98</v>
+        <v>309441570.85</v>
       </c>
     </row>
     <row r="4">
@@ -2214,7 +2340,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1654585820</v>
@@ -2223,43 +2349,43 @@
         <v>1654585820</v>
       </c>
       <c r="D5" t="n">
-        <v>24203977.7</v>
+        <v>23047428.34</v>
       </c>
       <c r="E5" t="n">
-        <v>1733025673.4</v>
+        <v>672921877.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2354020980.31</v>
+        <v>1229915698.63</v>
       </c>
       <c r="G5" t="n">
-        <v>419011356.49</v>
+        <v>478888491.95</v>
       </c>
       <c r="H5" t="n">
-        <v>1733025673.4</v>
+        <v>672921877.8</v>
       </c>
       <c r="I5" t="n">
-        <v>14305957.28</v>
+        <v>6983961.98</v>
       </c>
       <c r="J5" t="n">
-        <v>2353595485.51</v>
+        <v>1220694471.03</v>
       </c>
       <c r="K5" t="n">
-        <v>2353595485.51</v>
+        <v>1220694471.03</v>
       </c>
       <c r="L5" t="n">
-        <v>2401250237.68</v>
+        <v>1262267620.91</v>
       </c>
       <c r="M5" t="n">
-        <v>47654752.17</v>
+        <v>41573149.88</v>
       </c>
       <c r="N5" t="n">
-        <v>2353595485.51</v>
+        <v>1220694471.03</v>
       </c>
       <c r="O5" t="n">
-        <v>-6192552601.83</v>
+        <v>-7443173065.25</v>
       </c>
       <c r="P5" t="n">
-        <v>6991285559.02</v>
+        <v>7164346760.66</v>
       </c>
       <c r="Q5" t="n">
         <v>1654585820</v>
@@ -2268,361 +2394,235 @@
         <v>1654585820</v>
       </c>
       <c r="S5" t="n">
-        <v>366724092.11</v>
+        <v>503574361.78</v>
       </c>
       <c r="T5" t="n">
-        <v>24616759.61</v>
+        <v>15900594.64</v>
       </c>
       <c r="U5" t="n">
         <v>4618000</v>
       </c>
       <c r="V5" t="n">
-        <v>243886.61</v>
+        <v>1157296.67</v>
       </c>
       <c r="W5" t="n">
-        <v>5448915.72</v>
+        <v>3141335.99</v>
       </c>
       <c r="X5" t="n">
-        <v>14305957.28</v>
+        <v>6983961.98</v>
       </c>
       <c r="Y5" t="n">
-        <v>14305957.28</v>
+        <v>6983961.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>342107332.5</v>
+        <v>487673767.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>2334899.59</v>
+        <v>2226267.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>9898020.42</v>
+        <v>16063466.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>425494.8</v>
+        <v>9221227.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>279530165.73</v>
+        <v>428989894.82</v>
       </c>
       <c r="AE5" t="n">
-        <v>69431911.39</v>
+        <v>76905198.63</v>
       </c>
       <c r="AF5" t="n">
         <v>7768642.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>22890769.57</v>
+        <v>29291739.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>179438842.29</v>
+        <v>315024314.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>2767974329.79</v>
+        <v>1765841982.69</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2006855640.8</v>
+        <v>799279723.6</v>
       </c>
       <c r="AK5" t="n">
         <v>3176001.9</v>
       </c>
       <c r="AL5" t="n">
-        <v>7157289.37</v>
+        <v>5661921.96</v>
       </c>
       <c r="AM5" t="n">
-        <v>4747432.11</v>
+        <v>6643058.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>181566299.24</v>
+        <v>67892772.90000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>181566299.24</v>
+        <v>67892772.90000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>1096478240.11</v>
+        <v>83243428.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9067043.77</v>
+        <v>25740729.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>620569812.11</v>
+        <v>547772593.23</v>
       </c>
       <c r="AS5" t="n">
-        <v>4985443.94</v>
+        <v>3749785.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>615584368.17</v>
+        <v>544022808.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>84093522.19</v>
+        <v>59149217.73</v>
       </c>
       <c r="AV5" t="n">
-        <v>-53611893.76</v>
+        <v>-55697255.63</v>
       </c>
       <c r="AW5" t="n">
-        <v>137705415.95</v>
+        <v>114846473.36</v>
       </c>
       <c r="AX5" t="n">
-        <v>41831776.53</v>
+        <v>38967876.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>29727912.7</v>
+        <v>29253378.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>66145726.72</v>
+        <v>46625217.79</v>
       </c>
       <c r="BA5" t="n">
-        <v>761118688.99</v>
+        <v>966562259.09</v>
       </c>
       <c r="BB5" t="n">
-        <v>23453515.24</v>
+        <v>88252633.48999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>21491605.97</v>
+        <v>47633178.43</v>
       </c>
       <c r="BD5" t="n">
-        <v>24827793.76</v>
+        <v>16649936.92</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>6598713.56</v>
+        <v>3861586.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>16813684.97</v>
+        <v>12748195.26</v>
       </c>
       <c r="BH5" t="n">
-        <v>1415395.23</v>
+        <v>40155.41</v>
       </c>
       <c r="BI5" t="n">
-        <v>50308437.57</v>
+        <v>18474075.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>307815661.06</v>
+        <v>455083441.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>-147978214.55</v>
+        <v>-121849136.28</v>
       </c>
       <c r="BL5" t="n">
-        <v>455793875.61</v>
+        <v>576932577.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>333221675.39</v>
+        <v>340468993.21</v>
       </c>
       <c r="BN5" t="n">
-        <v>12000000</v>
+        <v>29725574.54</v>
       </c>
       <c r="BO5" t="n">
-        <v>321221675.39</v>
+        <v>310743418.67</v>
       </c>
       <c r="BP5" t="n">
-        <v>11780104.54</v>
+        <v>4370764.69</v>
       </c>
       <c r="BQ5" t="n">
-        <v>309441570.85</v>
+        <v>306372653.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1662283291</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1662283291</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16144050.86</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2065256003.59</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2687208070.75</v>
-      </c>
-      <c r="G6" t="n">
-        <v>974739557.42</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2065256003.59</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1853092.27</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2686465217.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2686465217.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2761320716.19</v>
-      </c>
-      <c r="M6" t="n">
-        <v>74855498.23999999</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2686465217.95</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-5911320653.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7024377847.29</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1662283291</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1662283291</v>
-      </c>
-      <c r="S6" t="n">
-        <v>824910761.0599999</v>
-      </c>
-      <c r="T6" t="n">
-        <v>458244305.55</v>
-      </c>
-      <c r="U6" t="n">
-        <v>453909241</v>
-      </c>
-      <c r="V6" t="n">
-        <v>265933.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2216038.58</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1853092.27</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1853092.27</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>366666455.51</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6323166.49</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>14290958.59</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>742852.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>267306786.35</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>60149180.48</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9091214.48</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19631124.13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>178435267.26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>3586231477.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2244825464.32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3176001.9</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>8349035.18</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>794630.9399999999</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>177153288.35</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>177153288.35</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1349193737.49</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>621209214.36</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2187926.81</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>619021287.55</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>84949556.09999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-51995866.19</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>136945422.29</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>28977791.49</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>31126135.05</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>76841495.75</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1341406012.93</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16099684.28</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>28059844.9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>24134107.28</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12068939.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>11292780.96</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>772386.72</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>67975085.45999999</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>220220873.8</v>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
-        <v>984916417.21</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>582068791.23</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>402847625.98</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>8968598.07</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>393879027.91</v>
-      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>-186840521.09</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>729941163.87</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2877,564 +2877,564 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-78892415.84</v>
+        <v>-71253878.83</v>
       </c>
       <c r="C2" t="n">
-        <v>-33056.37</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-6495724.3</v>
+        <v>-19029000.6</v>
       </c>
       <c r="F2" t="n">
-        <v>309776308.08</v>
+        <v>384528938.1</v>
       </c>
       <c r="G2" t="n">
-        <v>370144978.98</v>
+        <v>444440765.84</v>
       </c>
       <c r="H2" t="n">
-        <v>1026271.27</v>
+        <v>-3078370.36</v>
       </c>
       <c r="I2" t="n">
-        <v>-61394942.17</v>
+        <v>-56833457.38</v>
       </c>
       <c r="J2" t="n">
-        <v>-31844898.93</v>
+        <v>-30554126.03</v>
       </c>
       <c r="K2" t="n">
-        <v>-13251433.44</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-281409.12</v>
-      </c>
+        <v>-3884426.03</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>8966943.630000001</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>8966943.630000001</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-33056.37</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>42846648.3</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>25945546.88</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-28339884.81</v>
+      </c>
       <c r="S2" t="n">
-        <v>32250676.7</v>
+        <v>56848775.94</v>
       </c>
       <c r="T2" t="n">
-        <v>32649676.7</v>
+        <v>72968775.94</v>
       </c>
       <c r="U2" t="n">
-        <v>-399000</v>
+        <v>-16120000</v>
       </c>
       <c r="V2" t="n">
-        <v>9959177.550000001</v>
+        <v>16462156.35</v>
       </c>
       <c r="W2" t="n">
-        <v>9959177.550000001</v>
+        <v>16462156.35</v>
       </c>
       <c r="X2" t="n">
-        <v>636794.05</v>
+        <v>-19025500.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>7132518.35</v>
+        <v>3500</v>
       </c>
       <c r="Z2" t="n">
-        <v>-6495724.3</v>
+        <v>-19029000.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>-72396691.54000001</v>
+        <v>-52224878.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>-262617716.38</v>
+        <v>-104046081.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1300464.52</v>
+        <v>-16749595.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>-187410286.64</v>
+        <v>-72950043.81999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>3058615.34</v>
+        <v>5892309.81</v>
       </c>
       <c r="AF2" t="n">
-        <v>-76965580.56</v>
+        <v>-20238752.68</v>
       </c>
       <c r="AG2" t="n">
-        <v>3577178.78</v>
+        <v>20217192.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>23414747.1</v>
+        <v>32447691.43</v>
       </c>
       <c r="AI2" t="n">
-        <v>809135.39</v>
+        <v>8518731.32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22605611.71</v>
+        <v>23928960.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>160158902.59</v>
+        <v>-148881365.37</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1979729.6</v>
+        <v>-98919.28</v>
       </c>
       <c r="AM2" t="n">
-        <v>-109840872.54</v>
+        <v>57239196.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>-72396691.54000001</v>
+        <v>-52224878.23</v>
       </c>
       <c r="AO2" t="n">
-        <v>-49380590.28</v>
+        <v>-28408302.13</v>
       </c>
       <c r="AP2" t="n">
-        <v>-2747781710.81</v>
+        <v>-1882297495.98</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-190805904.42</v>
+        <v>-269893753.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>-207384509.32</v>
+        <v>-208344589.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2349591297.07</v>
+        <v>-1404059153.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>2724765609.55</v>
+        <v>1858480919.88</v>
       </c>
       <c r="AU2" t="n">
-        <v>60421552.64</v>
+        <v>95330576.38</v>
       </c>
       <c r="AV2" t="n">
-        <v>2664344056.91</v>
+        <v>1763150343.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-7041211.85</v>
+        <v>-138896991.64</v>
       </c>
       <c r="C3" t="n">
-        <v>-180673.2</v>
+        <v>-221079.6</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-5954923.27</v>
+        <v>-12518066.57</v>
       </c>
       <c r="F3" t="n">
-        <v>370144978.98</v>
+        <v>320566999.17</v>
       </c>
       <c r="G3" t="n">
-        <v>320566999.17</v>
+        <v>384528938.1</v>
       </c>
       <c r="H3" t="n">
-        <v>152536.79</v>
+        <v>9946333.609999999</v>
       </c>
       <c r="I3" t="n">
-        <v>49425443.02</v>
+        <v>-73908272.54000001</v>
       </c>
       <c r="J3" t="n">
-        <v>93548512.37</v>
+        <v>-33416708.78</v>
       </c>
       <c r="K3" t="n">
-        <v>124042417.82</v>
+        <v>21968327.05</v>
       </c>
       <c r="L3" t="n">
-        <v>-3232.25</v>
+        <v>-5956.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-180673.2</v>
+        <v>-221079.6</v>
       </c>
       <c r="N3" t="n">
-        <v>-180673.2</v>
+        <v>-221079.6</v>
       </c>
       <c r="O3" t="n">
-        <v>-180673.2</v>
+        <v>-221079.6</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>-43036780.77</v>
+        <v>85887361.31</v>
       </c>
       <c r="R3" t="n">
-        <v>-39000000</v>
+        <v>9106851.210000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1853742.5</v>
+        <v>15095112.83</v>
       </c>
       <c r="T3" t="n">
-        <v>22153742.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-20300000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>15095112.83</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>74178363.84</v>
+      </c>
+      <c r="W3" t="n">
+        <v>74178363.84</v>
+      </c>
       <c r="X3" t="n">
-        <v>-5890523.27</v>
+        <v>-12492966.57</v>
       </c>
       <c r="Y3" t="n">
-        <v>64400</v>
+        <v>25100</v>
       </c>
       <c r="Z3" t="n">
-        <v>-5954923.27</v>
+        <v>-12518066.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1086288.58</v>
+        <v>-126378925.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>231933331.67</v>
+        <v>-74694322.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2902741.27</v>
+        <v>-801174.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>333926461.69</v>
+        <v>11255355.84</v>
       </c>
       <c r="AE3" t="n">
-        <v>92621.72</v>
+        <v>-693686.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>-99183010.47</v>
+        <v>-84454817.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>3938273.05</v>
+        <v>4335406.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>28354494.88</v>
+        <v>24897652.88</v>
       </c>
       <c r="AI3" t="n">
-        <v>1135371.38</v>
+        <v>1177305.38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27219123.5</v>
+        <v>23720347.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>495381777.84</v>
+        <v>24107359.16</v>
       </c>
       <c r="AL3" t="n">
-        <v>-11703981.46</v>
+        <v>45839.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1069573629.84</v>
+        <v>-261555420.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1086288.58</v>
+        <v>-126378925.07</v>
       </c>
       <c r="AO3" t="n">
-        <v>-76826746.83</v>
+        <v>-25444977.88</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2177685372.61</v>
+        <v>-1994554539.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-267150206.73</v>
+        <v>-205972385.54</v>
       </c>
       <c r="AR3" t="n">
-        <v>-217799403.38</v>
+        <v>-185870543.47</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1692735762.5</v>
+        <v>-1602711610.19</v>
       </c>
       <c r="AT3" t="n">
-        <v>2253425830.86</v>
+        <v>1893620592.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>161976206.43</v>
+        <v>93582649.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2091449624.43</v>
+        <v>1800037942.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-138896991.64</v>
+        <v>-7041211.85</v>
       </c>
       <c r="C4" t="n">
-        <v>-221079.6</v>
+        <v>-180673.2</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-12518066.57</v>
+        <v>-5954923.27</v>
       </c>
       <c r="F4" t="n">
+        <v>370144978.98</v>
+      </c>
+      <c r="G4" t="n">
         <v>320566999.17</v>
       </c>
-      <c r="G4" t="n">
-        <v>384528938.1</v>
-      </c>
       <c r="H4" t="n">
-        <v>9946333.609999999</v>
+        <v>152536.79</v>
       </c>
       <c r="I4" t="n">
-        <v>-73908272.54000001</v>
+        <v>49425443.02</v>
       </c>
       <c r="J4" t="n">
-        <v>-33416708.78</v>
+        <v>93548512.37</v>
       </c>
       <c r="K4" t="n">
-        <v>21968327.05</v>
+        <v>124042417.82</v>
       </c>
       <c r="L4" t="n">
-        <v>-5956.23</v>
+        <v>-3232.25</v>
       </c>
       <c r="M4" t="n">
-        <v>-221079.6</v>
+        <v>-180673.2</v>
       </c>
       <c r="N4" t="n">
-        <v>-221079.6</v>
+        <v>-180673.2</v>
       </c>
       <c r="O4" t="n">
-        <v>-221079.6</v>
+        <v>-180673.2</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>85887361.31</v>
+        <v>-43036780.77</v>
       </c>
       <c r="R4" t="n">
-        <v>9106851.210000001</v>
+        <v>-39000000</v>
       </c>
       <c r="S4" t="n">
-        <v>15095112.83</v>
+        <v>1853742.5</v>
       </c>
       <c r="T4" t="n">
-        <v>15095112.83</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>74178363.84</v>
-      </c>
-      <c r="W4" t="n">
-        <v>74178363.84</v>
-      </c>
+        <v>22153742.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-20300000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-12492966.57</v>
+        <v>-5890523.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>25100</v>
+        <v>64400</v>
       </c>
       <c r="Z4" t="n">
-        <v>-12518066.57</v>
+        <v>-5954923.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>-126378925.07</v>
+        <v>-1086288.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>-74694322.56</v>
+        <v>231933331.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>-801174.47</v>
+        <v>-2902741.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>11255355.84</v>
+        <v>333926461.69</v>
       </c>
       <c r="AE4" t="n">
-        <v>-693686.48</v>
+        <v>92621.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>-84454817.45</v>
+        <v>-99183010.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>4335406.73</v>
+        <v>3938273.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>24897652.88</v>
+        <v>28354494.88</v>
       </c>
       <c r="AI4" t="n">
-        <v>1177305.38</v>
+        <v>1135371.38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23720347.5</v>
+        <v>27219123.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>24107359.16</v>
+        <v>495381777.84</v>
       </c>
       <c r="AL4" t="n">
-        <v>45839.3</v>
+        <v>-11703981.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>-261555420.97</v>
+        <v>-1069573629.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>-126378925.07</v>
+        <v>-1086288.58</v>
       </c>
       <c r="AO4" t="n">
-        <v>-25444977.88</v>
+        <v>-76826746.83</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1994554539.2</v>
+        <v>-2177685372.61</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-205972385.54</v>
+        <v>-267150206.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>-185870543.47</v>
+        <v>-217799403.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1602711610.19</v>
+        <v>-1692735762.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1893620592.01</v>
+        <v>2253425830.86</v>
       </c>
       <c r="AU4" t="n">
-        <v>93582649.25</v>
+        <v>161976206.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>1800037942.76</v>
+        <v>2091449624.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-71253878.83</v>
+        <v>-78892415.84</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>-33056.37</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9000000</v>
+      </c>
       <c r="E5" t="n">
-        <v>-19029000.6</v>
+        <v>-6495724.3</v>
       </c>
       <c r="F5" t="n">
-        <v>384528938.1</v>
+        <v>309776308.08</v>
       </c>
       <c r="G5" t="n">
-        <v>444440765.84</v>
+        <v>370144978.98</v>
       </c>
       <c r="H5" t="n">
-        <v>-3078370.36</v>
+        <v>1026271.27</v>
       </c>
       <c r="I5" t="n">
-        <v>-56833457.38</v>
+        <v>-61394942.17</v>
       </c>
       <c r="J5" t="n">
-        <v>-30554126.03</v>
+        <v>-31844898.93</v>
       </c>
       <c r="K5" t="n">
-        <v>-3884426.03</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-13251433.44</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-281409.12</v>
+      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8966943.630000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8966943.630000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>-33056.37</v>
+      </c>
+      <c r="P5" t="n">
+        <v>9000000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>25945546.88</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-28339884.81</v>
-      </c>
+        <v>42846648.3</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>56848775.94</v>
+        <v>32250676.7</v>
       </c>
       <c r="T5" t="n">
-        <v>72968775.94</v>
+        <v>32649676.7</v>
       </c>
       <c r="U5" t="n">
-        <v>-16120000</v>
+        <v>-399000</v>
       </c>
       <c r="V5" t="n">
-        <v>16462156.35</v>
+        <v>9959177.550000001</v>
       </c>
       <c r="W5" t="n">
-        <v>16462156.35</v>
+        <v>9959177.550000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-19025500.6</v>
+        <v>636794.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>3500</v>
+        <v>7132518.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>-19029000.6</v>
+        <v>-6495724.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>-52224878.23</v>
+        <v>-72396691.54000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>-104046081.8</v>
+        <v>-262617716.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>-16749595.11</v>
+        <v>-1300464.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>-72950043.81999999</v>
+        <v>-187410286.64</v>
       </c>
       <c r="AE5" t="n">
-        <v>5892309.81</v>
+        <v>3058615.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>-20238752.68</v>
+        <v>-76965580.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>20217192.08</v>
+        <v>3577178.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>32447691.43</v>
+        <v>23414747.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>8518731.32</v>
+        <v>809135.39</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23928960.11</v>
+        <v>22605611.71</v>
       </c>
       <c r="AK5" t="n">
-        <v>-148881365.37</v>
+        <v>160158902.59</v>
       </c>
       <c r="AL5" t="n">
-        <v>-98919.28</v>
+        <v>-1979729.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>57239196.37</v>
+        <v>-109840872.54</v>
       </c>
       <c r="AN5" t="n">
-        <v>-52224878.23</v>
+        <v>-72396691.54000001</v>
       </c>
       <c r="AO5" t="n">
-        <v>-28408302.13</v>
+        <v>-49380590.28</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1882297495.98</v>
+        <v>-2747781710.81</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-269893753.08</v>
+        <v>-190805904.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>-208344589.5</v>
+        <v>-207384509.32</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1404059153.4</v>
+        <v>-2349591297.07</v>
       </c>
       <c r="AT5" t="n">
-        <v>1858480919.88</v>
+        <v>2724765609.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>95330576.38</v>
+        <v>60421552.64</v>
       </c>
       <c r="AV5" t="n">
-        <v>1763150343.5</v>
+        <v>2664344056.91</v>
       </c>
     </row>
   </sheetData>
@@ -3448,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP2"/>
+  <dimension ref="A1:EN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3479,705 +3479,695 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>website</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>industryKey</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>industryDisp</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>industryKey</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>industryDisp</t>
+          <t>sectorKey</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sectorDisp</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>sectorKey</t>
+          <t>longBusinessSummary</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>sectorDisp</t>
+          <t>fullTimeEmployees</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>longBusinessSummary</t>
+          <t>companyOfficers</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>fullTimeEmployees</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>companyOfficers</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>open</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>exDividendDate</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>forwardPE</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>forwardPE</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>forwardEps</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>forwardEps</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
       <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4186,12 +4176,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tower T4, Damei Center</t>
+          <t>Building 9, Innovation Workshop</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Floor 16 No. 7, Qingnian Road Chaoyang District</t>
+          <t>E9 Zone, Kangzhong Street Chaoyang District</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4201,7 +4191,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>100123</t>
+          <t>100121</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4211,17 +4201,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86 10 8792 6860</t>
+          <t>https://www.tianyushuke.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>86 10 8792 6860</t>
+          <t>Electronic Gaming &amp; Multimedia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.tianyushuke.com</t>
+          <t>electronic-gaming-multimedia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4231,12 +4221,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>electronic-gaming-multimedia</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Electronic Gaming &amp; Multimedia</t>
+          <t>communication-services</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -4246,462 +4236,452 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>communication-services</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
+          <t>Tianyu Digital Technology Group Co.,Ltd. engages in the development and operation of online games in China. The company offers web-based online games and mobile online games. It also provides Aisi Assistant, an Apple phone assistant; and SunVy Poker. In addition, the company is involved in the provision of mobile internet advertising and technical consulting services; and development and operation of mobile application distribution platforms. The company was formerly known as Tianyu Digital Technology (Dalian) Group Co., Ltd. and changed its name to Tianyu Digital Technology Group Co.,Ltd. in March 2026. The company was founded in 2003 and is headquartered in Beijing, China.</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2238</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Tianyu Digital Technology Group Co.,Ltd. engages in the e-sport games and data traffic businesses in China. The company develops and operates online games, including web online games and mobile online games. It is also involved in the provision of internet and mobile internet advertising services. In addition, the company develops and operates mobile application distribution platforms; and offers technical consulting services. The company was formerly known as Tianyu Digital Technology (Dalian) Group Co., Ltd. and changed its name to Tianyu Digital Technology Group Co.,Ltd. in March 2026. The company was founded in 2003 and is headquartered in Beijing, China.</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>2238</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
           <t>[{'maxAge': 1, 'name': 'Mr. Han  He', 'age': 37, 'title': 'GM &amp; Non-Independent Director', 'yearBorn': 1988, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Zhu  Shang', 'age': 50, 'title': 'Administrative Director', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuping  Liu', 'age': 59, 'title': 'Deputy GM &amp; Director', 'yearBorn': 1966, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Di  Liu', 'age': 42, 'title': 'Board Secretary &amp; Non-Independent Director', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hongfeng  Zhang', 'age': 48, 'title': 'Deputy General Manager', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guanbo  Liu', 'age': 39, 'title': 'Deputy General Manager', 'yearBorn': 1986, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ting Ting  Guan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="Q2" t="n">
+        <v>86400</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
       <c r="S2" t="n">
-        <v>86400</v>
+        <v>7.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>7.15</v>
       </c>
       <c r="U2" t="n">
-        <v>7.13</v>
+        <v>8.09</v>
       </c>
       <c r="V2" t="n">
-        <v>6.77</v>
+        <v>8.5</v>
       </c>
       <c r="W2" t="n">
-        <v>6.97</v>
+        <v>7.73</v>
       </c>
       <c r="X2" t="n">
-        <v>7.38</v>
+        <v>7.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.13</v>
+        <v>8.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.77</v>
+        <v>8.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.97</v>
+        <v>1530489600</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>288717634</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>288717634</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>154330762</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>338763367</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>338763367</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>14063979520</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12789948388</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.5747576</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.5588</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.70035</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13654509568</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.01115</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1569374650</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1654585820</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.05827</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.044320002</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1654585820</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>10.228641</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>4.769</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-23851698</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>6.383</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>268.171</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.2840532</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BV2" t="n">
         <v>1530489600</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BX2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>570525696</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>50917084</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>135579456</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>2139087232</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>9.679</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.013200001</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.00409</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>601011648</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>20703836</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>193985312</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.28097</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.120620005</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CY2" t="b">
         <v>0</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>143</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>239145113</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>239145113</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>98523319</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>233398821</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>233398821</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1782111840</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_261221062</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="DJ2" t="n">
+        <v>9.96119</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Tianyu Digital Technology Group Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>8.09 - 8.5</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>154330762</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>3.1399999</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.5858208499999999</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>5.36 - 8.87</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.3699999</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.04171363</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>28.405321</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1619780340</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1619780340</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1.9411998</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.29596874</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1.7996502</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.26859048</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>TIANYU DIGITAL TECH GP CO LTD</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>Dalian Zeus Entertainment Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
         <v>0</v>
       </c>
-      <c r="AP2" t="n">
-        <v>11830289408</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11830288613</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>125.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.5305314</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.093</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.7188</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="EK2" t="b">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="BB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11420818432</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.01115</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1570814140</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1654585820</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.05827</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.044320002</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1654585820</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>8.604092</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.769</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-23851698</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>5.339</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>224.302</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.12068963</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.27697718</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1530489600</v>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BZ2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CB2" t="n">
-        <v>570525696</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>50917084</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>135579456</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>2139087232</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>9.679</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.013200001</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>-0.00409</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>601011648</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>20703836</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>193985312</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>4.719</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.28097</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>0.0238</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.120620005</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>002354.SZ</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.2805046</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>finmb_261221062</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>TIANYU DIGITAL TECH GP CO LTD</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.43120003</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.06417813</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Dalian Zeus Entertainment Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
+      <c r="EL2" t="n">
         <v>1265679000000</v>
       </c>
-      <c r="DV2" t="n">
-        <v>0.01999998</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>6.97 - 7.38</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>98523319</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.3339552</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>5.36 - 8.67</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.17531718</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>12.068963</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1619780340</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1619780340</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.0570002</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.17347778</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="EM2" t="n">
-        <v>1780038252</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Tianyu Digital Technology Group Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr"/>
+        <v>0.77</v>
+      </c>
+      <c r="EN2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
